--- a/docs/training/files/basic_excel.xlsx
+++ b/docs/training/files/basic_excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NzWin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NzWin\dev\ai\epkotsoftware.github.io\docs\training\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47BF050A-2B30-4CD7-BF53-A8453127DD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD860AF1-DF1D-44B9-A281-D51787DB8269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="300" windowWidth="40680" windowHeight="30780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="40680" windowHeight="30780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="売上管理票" sheetId="1" r:id="rId1"/>
@@ -272,9 +272,6 @@
     <t>Invoice</t>
   </si>
   <si>
-    <t>御　請　求　書</t>
-  </si>
-  <si>
     <t>下記のとおりにご請求申し上げます。</t>
   </si>
   <si>
@@ -490,6 +487,13 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>御　請　求　書(任意課題)</t>
+    <rPh sb="8" eb="12">
+      <t>ニンイカダイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -515,7 +519,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -523,7 +527,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -531,14 +535,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -546,7 +550,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -561,7 +565,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -570,14 +574,14 @@
       <u/>
       <sz val="12"/>
       <color theme="11"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -591,7 +595,7 @@
     </font>
     <font>
       <sz val="18"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -599,7 +603,7 @@
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -708,7 +712,7 @@
     </font>
     <font>
       <sz val="15"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -716,7 +720,7 @@
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="メイリオ"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1204,7 +1208,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1437,9 +1441,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="50" applyFont="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1463,6 +1464,51 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1504,51 +1550,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -2477,67 +2478,67 @@
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="89"/>
+      <c r="O27" s="89"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="C28" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="90"/>
-      <c r="K27" s="90"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="90"/>
-      <c r="O27" s="90"/>
-      <c r="P27" s="5"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="C28" s="89" t="s">
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="89"/>
+      <c r="N28" s="89"/>
+      <c r="O28" s="89"/>
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="C29" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="90"/>
-      <c r="K28" s="90"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="90"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="5"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="C29" s="89" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="90"/>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="90"/>
-      <c r="O29" s="90"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="89"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="5"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="P31" s="86"/>
+      <c r="P31" s="85"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="P32" s="87"/>
+      <c r="P32" s="86"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -2560,16 +2561,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94" t="s">
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="96"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="95"/>
     </row>
     <row r="3" spans="2:10" s="19" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3"/>
@@ -2586,11 +2587,11 @@
         <v>31</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H3" s="79"/>
       <c r="I3" s="84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -2609,9 +2610,9 @@
       <c r="F4" s="78"/>
       <c r="G4" s="78"/>
       <c r="H4" s="78"/>
-      <c r="I4" s="85"/>
+      <c r="I4" s="78"/>
       <c r="J4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -2630,7 +2631,7 @@
       <c r="F5" s="78"/>
       <c r="G5" s="78"/>
       <c r="H5" s="78"/>
-      <c r="I5" s="85"/>
+      <c r="I5" s="78"/>
     </row>
     <row r="6" spans="2:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="18" t="s">
@@ -2648,7 +2649,7 @@
       <c r="F6" s="78"/>
       <c r="G6" s="78"/>
       <c r="H6" s="78"/>
-      <c r="I6" s="85"/>
+      <c r="I6" s="78"/>
     </row>
     <row r="7" spans="2:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="18" t="s">
@@ -2666,7 +2667,7 @@
       <c r="F7" s="78"/>
       <c r="G7" s="78"/>
       <c r="H7" s="78"/>
-      <c r="I7" s="85"/>
+      <c r="I7" s="78"/>
     </row>
     <row r="8" spans="2:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="18" t="s">
@@ -2684,7 +2685,7 @@
       <c r="F8" s="78"/>
       <c r="G8" s="78"/>
       <c r="H8" s="78"/>
-      <c r="I8" s="85"/>
+      <c r="I8" s="78"/>
     </row>
     <row r="9" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.2">
@@ -2731,46 +2732,46 @@
   <sheetData>
     <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:11" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-    </row>
-    <row r="3" spans="2:11" ht="45.75" x14ac:dyDescent="0.9">
-      <c r="B3" s="106" t="s">
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+    </row>
+    <row r="3" spans="2:11" ht="43.5" x14ac:dyDescent="0.95">
+      <c r="B3" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+    </row>
+    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-    </row>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="108" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
     </row>
     <row r="5" spans="2:11" ht="33" x14ac:dyDescent="0.15">
       <c r="B5" s="24"/>
@@ -2785,24 +2786,24 @@
       <c r="K5" s="25"/>
     </row>
     <row r="6" spans="2:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B6" s="110" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
+      <c r="B6" s="124" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
       <c r="G6" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="25"/>
       <c r="I6" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="99"/>
+        <v>38</v>
+      </c>
+      <c r="J6" s="125" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="113"/>
     </row>
     <row r="7" spans="2:11" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B7" s="25"/>
@@ -2817,10 +2818,10 @@
       <c r="K7" s="28"/>
     </row>
     <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="112" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="112"/>
+      <c r="B8" s="126" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="126"/>
       <c r="D8" s="29"/>
       <c r="E8" s="29"/>
       <c r="F8" s="29"/>
@@ -2837,10 +2838,10 @@
       </c>
     </row>
     <row r="9" spans="2:11" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="B9" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="97"/>
+      <c r="B9" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="111"/>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
@@ -2864,7 +2865,7 @@
     </row>
     <row r="11" spans="2:11" ht="36" thickBot="1" x14ac:dyDescent="0.85">
       <c r="B11" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="36">
         <f>H33+F11</f>
@@ -2872,11 +2873,11 @@
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="77"/>
       <c r="G11" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H11" s="25"/>
       <c r="I11" s="40"/>
@@ -2896,50 +2897,50 @@
       <c r="K12" s="25"/>
     </row>
     <row r="13" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="112" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="41" t="s">
+      <c r="E13" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="F13" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="G13" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="H13" s="42" t="s">
         <v>47</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>48</v>
       </c>
       <c r="I13" s="43"/>
       <c r="J13" s="44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K13" s="45"/>
     </row>
     <row r="14" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="101"/>
+      <c r="B14" s="114" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="115"/>
       <c r="D14" s="46"/>
       <c r="E14" s="47"/>
       <c r="F14" s="48"/>
       <c r="G14" s="49"/>
       <c r="H14" s="47"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="101"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="115"/>
     </row>
     <row r="15" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="114"/>
+      <c r="B15" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="104"/>
       <c r="D15" s="50"/>
       <c r="E15" s="51">
         <v>300000</v>
@@ -2948,21 +2949,21 @@
         <v>1</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="54">
         <f>E15*F15</f>
         <v>300000</v>
       </c>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="117"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="109"/>
     </row>
     <row r="16" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="118" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="114"/>
+      <c r="B16" s="103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="104"/>
       <c r="D16" s="50"/>
       <c r="E16" s="51">
         <v>45000</v>
@@ -2971,21 +2972,21 @@
         <v>5</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H16" s="54">
         <f>E16*F16</f>
         <v>225000</v>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="117"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="109"/>
     </row>
     <row r="17" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="118" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="114"/>
+      <c r="B17" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="104"/>
       <c r="D17" s="46"/>
       <c r="E17" s="51">
         <v>1358</v>
@@ -2994,59 +2995,59 @@
         <v>1</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="54">
         <f>E17*F17</f>
         <v>1358</v>
       </c>
-      <c r="I17" s="115" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="116"/>
-      <c r="K17" s="117"/>
+      <c r="I17" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="108"/>
+      <c r="K17" s="109"/>
     </row>
     <row r="18" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B18" s="118" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="114"/>
+      <c r="B18" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="104"/>
       <c r="D18" s="46"/>
       <c r="E18" s="51"/>
       <c r="F18" s="55"/>
       <c r="G18" s="53"/>
       <c r="H18" s="54"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="117"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="109"/>
     </row>
     <row r="19" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B19" s="118"/>
-      <c r="C19" s="114"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="104"/>
       <c r="D19" s="46"/>
       <c r="E19" s="51"/>
       <c r="F19" s="56"/>
       <c r="G19" s="53"/>
       <c r="H19" s="54"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="117"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="109"/>
     </row>
     <row r="20" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B20" s="118"/>
-      <c r="C20" s="114"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="104"/>
       <c r="D20" s="46"/>
       <c r="E20" s="51"/>
       <c r="F20" s="57"/>
       <c r="G20" s="53"/>
       <c r="H20" s="54"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="117"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="109"/>
     </row>
     <row r="21" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B21" s="118"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="104"/>
       <c r="D21" s="46"/>
       <c r="E21" s="51"/>
       <c r="F21" s="57"/>
@@ -3057,8 +3058,8 @@
       <c r="K21" s="60"/>
     </row>
     <row r="22" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B22" s="118"/>
-      <c r="C22" s="114"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
       <c r="D22" s="50"/>
       <c r="E22" s="51"/>
       <c r="F22" s="61"/>
@@ -3069,8 +3070,8 @@
       <c r="K22" s="60"/>
     </row>
     <row r="23" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B23" s="118"/>
-      <c r="C23" s="114"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="104"/>
       <c r="D23" s="50"/>
       <c r="E23" s="51"/>
       <c r="F23" s="57"/>
@@ -3081,8 +3082,8 @@
       <c r="K23" s="60"/>
     </row>
     <row r="24" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B24" s="118"/>
-      <c r="C24" s="114"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="50"/>
       <c r="E24" s="51"/>
       <c r="F24" s="57"/>
@@ -3093,8 +3094,8 @@
       <c r="K24" s="60"/>
     </row>
     <row r="25" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B25" s="118"/>
-      <c r="C25" s="114"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
       <c r="D25" s="50"/>
       <c r="E25" s="51"/>
       <c r="F25" s="57"/>
@@ -3105,8 +3106,8 @@
       <c r="K25" s="60"/>
     </row>
     <row r="26" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B26" s="118"/>
-      <c r="C26" s="114"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="104"/>
       <c r="D26" s="62"/>
       <c r="E26" s="63"/>
       <c r="F26" s="64"/>
@@ -3117,8 +3118,8 @@
       <c r="K26" s="60"/>
     </row>
     <row r="27" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B27" s="118"/>
-      <c r="C27" s="114"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="104"/>
       <c r="D27" s="50"/>
       <c r="E27" s="51"/>
       <c r="F27" s="51"/>
@@ -3129,8 +3130,8 @@
       <c r="K27" s="60"/>
     </row>
     <row r="28" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B28" s="118"/>
-      <c r="C28" s="114"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="104"/>
       <c r="D28" s="50"/>
       <c r="E28" s="51"/>
       <c r="F28" s="51"/>
@@ -3141,8 +3142,8 @@
       <c r="K28" s="60"/>
     </row>
     <row r="29" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B29" s="118"/>
-      <c r="C29" s="114"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="104"/>
       <c r="D29" s="50"/>
       <c r="E29" s="51"/>
       <c r="F29" s="51"/>
@@ -3153,8 +3154,8 @@
       <c r="K29" s="60"/>
     </row>
     <row r="30" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B30" s="118"/>
-      <c r="C30" s="114"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="104"/>
       <c r="D30" s="50"/>
       <c r="E30" s="51"/>
       <c r="F30" s="51"/>
@@ -3165,39 +3166,39 @@
       <c r="K30" s="60"/>
     </row>
     <row r="31" spans="2:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="B31" s="118"/>
-      <c r="C31" s="114"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
       <c r="D31" s="50"/>
       <c r="E31" s="51"/>
       <c r="F31" s="51"/>
       <c r="G31" s="53"/>
       <c r="H31" s="54"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="126"/>
-      <c r="K31" s="127"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="107"/>
     </row>
     <row r="32" spans="2:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="119"/>
-      <c r="C32" s="120"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="97"/>
       <c r="D32" s="66"/>
       <c r="E32" s="67"/>
       <c r="F32" s="68"/>
       <c r="G32" s="69"/>
       <c r="H32" s="68"/>
-      <c r="I32" s="121"/>
-      <c r="J32" s="122"/>
-      <c r="K32" s="123"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="100"/>
     </row>
     <row r="33" spans="2:23" ht="23.25" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="124" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="125"/>
+      <c r="B33" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="102"/>
       <c r="D33" s="70"/>
       <c r="E33" s="71"/>
       <c r="F33" s="72"/>
       <c r="G33" s="73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="71">
         <f>SUM(H14:H32)</f>
@@ -3220,12 +3221,12 @@
       <c r="K34" s="28"/>
     </row>
     <row r="35" spans="2:23" ht="18" x14ac:dyDescent="0.2">
-      <c r="H35" s="91">
+      <c r="H35" s="90">
         <f>H33*0.08</f>
         <v>42108.639999999999</v>
       </c>
       <c r="I35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N35" s="80"/>
       <c r="O35" s="80"/>
@@ -3239,25 +3240,32 @@
       <c r="W35" s="80"/>
     </row>
     <row r="36" spans="2:23" ht="18" x14ac:dyDescent="0.2">
-      <c r="H36" s="92">
+      <c r="H36" s="91">
         <f>H33+H35</f>
         <v>568466.64</v>
       </c>
       <c r="I36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="I17:K17"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="I18:K18"/>
@@ -3270,22 +3278,15 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:K31"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
